--- a/research/traditional_assets/database/data/canada/canada_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1815</v>
+        <v>0.175</v>
       </c>
       <c r="E2">
-        <v>0.631</v>
+        <v>0.7809999999999999</v>
       </c>
       <c r="G2">
-        <v>0.03638740380439235</v>
+        <v>0.2808145766345123</v>
       </c>
       <c r="H2">
-        <v>0.03638740380439235</v>
+        <v>0.2808145766345123</v>
       </c>
       <c r="I2">
-        <v>0.183770898732436</v>
+        <v>0.1082529474812433</v>
       </c>
       <c r="J2">
-        <v>0.1663955251615016</v>
+        <v>0.1082529474812433</v>
       </c>
       <c r="K2">
-        <v>3380.49</v>
+        <v>2.32</v>
       </c>
       <c r="L2">
-        <v>0.1306239364193209</v>
+        <v>0.2486602357984994</v>
       </c>
       <c r="M2">
-        <v>463.5</v>
+        <v>0.512</v>
       </c>
       <c r="N2">
-        <v>0.03546560563164741</v>
+        <v>0.03710144927536232</v>
       </c>
       <c r="O2">
-        <v>0.1371103005777269</v>
+        <v>0.2206896551724138</v>
       </c>
       <c r="P2">
-        <v>272.1</v>
+        <v>0.512</v>
       </c>
       <c r="Q2">
-        <v>0.02082026168796389</v>
+        <v>0.03710144927536232</v>
       </c>
       <c r="R2">
-        <v>0.08049128972427075</v>
+        <v>0.2206896551724138</v>
       </c>
       <c r="S2">
-        <v>191.4</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.4129449838187702</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>10667.576</v>
+        <v>1.45</v>
       </c>
       <c r="V2">
-        <v>0.8162503634555055</v>
+        <v>0.1050724637681159</v>
       </c>
       <c r="W2">
-        <v>0.4782681810430618</v>
+        <v>0.5672371638141809</v>
       </c>
       <c r="X2">
-        <v>0.05043089572115386</v>
+        <v>0.07579642866085565</v>
       </c>
       <c r="Y2">
-        <v>0.4278372853219079</v>
+        <v>0.4914407351533252</v>
       </c>
       <c r="Z2">
-        <v>1.521177317214771</v>
+        <v>2.163729128014843</v>
       </c>
       <c r="AA2">
-        <v>0.2790600053178331</v>
+        <v>0.2342300556586271</v>
       </c>
       <c r="AB2">
-        <v>0.04403606339566943</v>
+        <v>0.07480438594593243</v>
       </c>
       <c r="AC2">
-        <v>0.2350239419221637</v>
+        <v>0.1594256697126947</v>
       </c>
       <c r="AD2">
-        <v>7952.98</v>
+        <v>0.408</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7952.98</v>
+        <v>0.408</v>
       </c>
       <c r="AG2">
-        <v>-2714.596</v>
+        <v>-1.042</v>
       </c>
       <c r="AH2">
-        <v>0.3783173611619838</v>
+        <v>0.02871621621621621</v>
       </c>
       <c r="AI2">
-        <v>0.2829257290523085</v>
+        <v>0.05715886803026057</v>
       </c>
       <c r="AJ2">
-        <v>-0.2621682522721733</v>
+        <v>-0.08167424361185138</v>
       </c>
       <c r="AK2">
-        <v>-0.1556337719705606</v>
+        <v>-0.1831926863572433</v>
       </c>
       <c r="AL2">
-        <v>510.748</v>
+        <v>0.016</v>
       </c>
       <c r="AM2">
-        <v>510.748</v>
+        <v>0.016</v>
       </c>
       <c r="AN2">
-        <v>1.544058089191761</v>
+        <v>0.2193548387096774</v>
       </c>
       <c r="AO2">
-        <v>9.311656629100849</v>
+        <v>63.125</v>
       </c>
       <c r="AP2">
-        <v>-0.5270343836760053</v>
+        <v>-0.5602150537634408</v>
       </c>
       <c r="AQ2">
-        <v>9.311656629100849</v>
+        <v>63.125</v>
       </c>
     </row>
     <row r="3">
@@ -722,249 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.153</v>
+        <v>0.175</v>
+      </c>
+      <c r="E3">
+        <v>0.7809999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2157534246575342</v>
+        <v>0.2808145766345123</v>
       </c>
       <c r="H3">
-        <v>0.2157534246575342</v>
+        <v>0.2808145766345123</v>
       </c>
       <c r="I3">
-        <v>0.1267123287671233</v>
+        <v>0.1082529474812433</v>
       </c>
       <c r="J3">
-        <v>0.1267123287671233</v>
+        <v>0.1082529474812433</v>
       </c>
       <c r="K3">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="L3">
-        <v>0.1815068493150685</v>
+        <v>0.2486602357984994</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.512</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03710144927536232</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2206896551724138</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.512</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03710144927536232</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2206896551724138</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.476</v>
+        <v>1.45</v>
       </c>
       <c r="V3">
-        <v>0.02144144144144144</v>
+        <v>0.1050724637681159</v>
       </c>
       <c r="W3">
-        <v>0.6652719665271967</v>
+        <v>0.5672371638141809</v>
       </c>
       <c r="X3">
-        <v>0.04417864325073362</v>
+        <v>0.07579642866085565</v>
       </c>
       <c r="Y3">
-        <v>0.621093323276463</v>
+        <v>0.4914407351533252</v>
       </c>
       <c r="Z3">
-        <v>2.615706180949537</v>
+        <v>2.163729128014843</v>
       </c>
       <c r="AA3">
-        <v>0.3314422215586743</v>
+        <v>0.2342300556586271</v>
       </c>
       <c r="AB3">
-        <v>0.043781054359468</v>
+        <v>0.07480438594593243</v>
       </c>
       <c r="AC3">
-        <v>0.2876611671992063</v>
+        <v>0.1594256697126947</v>
       </c>
       <c r="AD3">
-        <v>0.38</v>
+        <v>0.408</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.38</v>
+        <v>0.408</v>
       </c>
       <c r="AG3">
-        <v>-0.09599999999999997</v>
+        <v>-1.042</v>
       </c>
       <c r="AH3">
-        <v>0.01682905225863596</v>
+        <v>0.02871621621621621</v>
       </c>
       <c r="AI3">
-        <v>0.06574394463667819</v>
+        <v>0.05715886803026057</v>
       </c>
       <c r="AJ3">
-        <v>-0.004343105320304017</v>
+        <v>-0.08167424361185138</v>
       </c>
       <c r="AK3">
-        <v>-0.01809954751131221</v>
+        <v>-0.1831926863572433</v>
       </c>
       <c r="AL3">
-        <v>0.048</v>
+        <v>0.016</v>
       </c>
       <c r="AM3">
-        <v>0.048</v>
+        <v>0.016</v>
       </c>
       <c r="AN3">
-        <v>0.2111111111111111</v>
+        <v>0.2193548387096774</v>
       </c>
       <c r="AO3">
-        <v>23.125</v>
+        <v>63.125</v>
       </c>
       <c r="AP3">
-        <v>-0.05333333333333332</v>
+        <v>-0.5602150537634408</v>
       </c>
       <c r="AQ3">
-        <v>23.125</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.21</v>
-      </c>
-      <c r="E4">
-        <v>0.631</v>
-      </c>
-      <c r="G4">
-        <v>0.0363266694497271</v>
-      </c>
-      <c r="H4">
-        <v>0.0363266694497271</v>
-      </c>
-      <c r="I4">
-        <v>0.1837902190887023</v>
-      </c>
-      <c r="J4">
-        <v>0.1490358185021373</v>
-      </c>
-      <c r="K4">
-        <v>3378.9</v>
-      </c>
-      <c r="L4">
-        <v>0.1306067071756575</v>
-      </c>
-      <c r="M4">
-        <v>463.5</v>
-      </c>
-      <c r="N4">
-        <v>0.03552595272403961</v>
-      </c>
-      <c r="O4">
-        <v>0.1371748202077599</v>
-      </c>
-      <c r="P4">
-        <v>272.1</v>
-      </c>
-      <c r="Q4">
-        <v>0.02085568875126468</v>
-      </c>
-      <c r="R4">
-        <v>0.08052916629672378</v>
-      </c>
-      <c r="S4">
-        <v>191.4</v>
-      </c>
-      <c r="T4">
-        <v>0.4129449838187702</v>
-      </c>
-      <c r="U4">
-        <v>10667.1</v>
-      </c>
-      <c r="V4">
-        <v>0.8176027838243861</v>
-      </c>
-      <c r="W4">
-        <v>0.291264395558927</v>
-      </c>
-      <c r="X4">
-        <v>0.0566831481915741</v>
-      </c>
-      <c r="Y4">
-        <v>0.2345812473673529</v>
-      </c>
-      <c r="Z4">
-        <v>1.520961815456069</v>
-      </c>
-      <c r="AA4">
-        <v>0.2266777890769919</v>
-      </c>
-      <c r="AB4">
-        <v>0.04429107243187087</v>
-      </c>
-      <c r="AC4">
-        <v>0.1823867166451211</v>
-      </c>
-      <c r="AD4">
-        <v>7952.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>7952.6</v>
-      </c>
-      <c r="AG4">
-        <v>-2714.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.3787060582683315</v>
-      </c>
-      <c r="AI4">
-        <v>0.2829703956732138</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.2627198203691337</v>
-      </c>
-      <c r="AK4">
-        <v>-0.1556756074760995</v>
-      </c>
-      <c r="AL4">
-        <v>510.7</v>
-      </c>
-      <c r="AM4">
-        <v>510.7</v>
-      </c>
-      <c r="AN4">
-        <v>1.544524073102993</v>
-      </c>
-      <c r="AO4">
-        <v>9.310358331701586</v>
-      </c>
-      <c r="AP4">
-        <v>-0.5271999844627008</v>
-      </c>
-      <c r="AQ4">
-        <v>9.310358331701586</v>
+        <v>63.125</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_general.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.175</v>
-      </c>
-      <c r="E2">
-        <v>0.7809999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="G2">
-        <v>0.2808145766345123</v>
+        <v>0.1118811881188119</v>
       </c>
       <c r="H2">
-        <v>0.2808145766345123</v>
+        <v>0.1118811881188119</v>
       </c>
       <c r="I2">
-        <v>0.1082529474812433</v>
+        <v>-0.001584158415841584</v>
       </c>
       <c r="J2">
-        <v>0.1082529474812433</v>
+        <v>-0.001584158415841584</v>
       </c>
       <c r="K2">
-        <v>2.32</v>
+        <v>-0.229</v>
       </c>
       <c r="L2">
-        <v>0.2486602357984994</v>
+        <v>-0.02267326732673268</v>
       </c>
       <c r="M2">
-        <v>0.512</v>
+        <v>0.26</v>
       </c>
       <c r="N2">
-        <v>0.03710144927536232</v>
+        <v>0.02203389830508475</v>
       </c>
       <c r="O2">
-        <v>0.2206896551724138</v>
+        <v>-1.135371179039301</v>
       </c>
       <c r="P2">
-        <v>0.512</v>
+        <v>0.26</v>
       </c>
       <c r="Q2">
-        <v>0.03710144927536232</v>
+        <v>0.02203389830508475</v>
       </c>
       <c r="R2">
-        <v>0.2206896551724138</v>
+        <v>-1.135371179039301</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V2">
-        <v>0.1050724637681159</v>
+        <v>0.1211864406779661</v>
       </c>
       <c r="W2">
-        <v>0.5672371638141809</v>
+        <v>-0.04141048824593128</v>
       </c>
       <c r="X2">
-        <v>0.07579642866085565</v>
+        <v>0.06795996682593528</v>
       </c>
       <c r="Y2">
-        <v>0.4914407351533252</v>
+        <v>-0.1093704550718666</v>
       </c>
       <c r="Z2">
-        <v>2.163729128014843</v>
+        <v>2.111204013377926</v>
       </c>
       <c r="AA2">
-        <v>0.2342300556586271</v>
+        <v>-0.00334448160535117</v>
       </c>
       <c r="AB2">
-        <v>0.07480438594593243</v>
+        <v>0.06721407556188808</v>
       </c>
       <c r="AC2">
-        <v>0.1594256697126947</v>
+        <v>-0.07055855716723924</v>
       </c>
       <c r="AD2">
-        <v>0.408</v>
+        <v>0.295</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.408</v>
+        <v>0.295</v>
       </c>
       <c r="AG2">
-        <v>-1.042</v>
+        <v>-1.135</v>
       </c>
       <c r="AH2">
-        <v>0.02871621621621621</v>
+        <v>0.02439024390243902</v>
       </c>
       <c r="AI2">
-        <v>0.05715886803026057</v>
+        <v>0.04479878511769172</v>
       </c>
       <c r="AJ2">
-        <v>-0.08167424361185138</v>
+        <v>-0.1064228785747773</v>
       </c>
       <c r="AK2">
-        <v>-0.1831926863572433</v>
+        <v>-0.2201745877788555</v>
       </c>
       <c r="AL2">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="AM2">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="AN2">
-        <v>0.2193548387096774</v>
+        <v>0.3628536285362854</v>
       </c>
       <c r="AO2">
-        <v>63.125</v>
+        <v>-0.8</v>
       </c>
       <c r="AP2">
-        <v>-0.5602150537634408</v>
+        <v>-1.396063960639607</v>
       </c>
       <c r="AQ2">
-        <v>63.125</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.175</v>
-      </c>
-      <c r="E3">
-        <v>0.7809999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="G3">
-        <v>0.2808145766345123</v>
+        <v>0.1118811881188119</v>
       </c>
       <c r="H3">
-        <v>0.2808145766345123</v>
+        <v>0.1118811881188119</v>
       </c>
       <c r="I3">
-        <v>0.1082529474812433</v>
+        <v>-0.001584158415841584</v>
       </c>
       <c r="J3">
-        <v>0.1082529474812433</v>
+        <v>-0.001584158415841584</v>
       </c>
       <c r="K3">
-        <v>2.32</v>
+        <v>-0.229</v>
       </c>
       <c r="L3">
-        <v>0.2486602357984994</v>
+        <v>-0.02267326732673268</v>
       </c>
       <c r="M3">
-        <v>0.512</v>
+        <v>0.26</v>
       </c>
       <c r="N3">
-        <v>0.03710144927536232</v>
+        <v>0.02203389830508475</v>
       </c>
       <c r="O3">
-        <v>0.2206896551724138</v>
+        <v>-1.135371179039301</v>
       </c>
       <c r="P3">
-        <v>0.512</v>
+        <v>0.26</v>
       </c>
       <c r="Q3">
-        <v>0.03710144927536232</v>
+        <v>0.02203389830508475</v>
       </c>
       <c r="R3">
-        <v>0.2206896551724138</v>
+        <v>-1.135371179039301</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V3">
-        <v>0.1050724637681159</v>
+        <v>0.1211864406779661</v>
       </c>
       <c r="W3">
-        <v>0.5672371638141809</v>
+        <v>-0.04141048824593128</v>
       </c>
       <c r="X3">
-        <v>0.07579642866085565</v>
+        <v>0.06795996682593528</v>
       </c>
       <c r="Y3">
-        <v>0.4914407351533252</v>
+        <v>-0.1093704550718666</v>
       </c>
       <c r="Z3">
-        <v>2.163729128014843</v>
+        <v>2.111204013377926</v>
       </c>
       <c r="AA3">
-        <v>0.2342300556586271</v>
+        <v>-0.00334448160535117</v>
       </c>
       <c r="AB3">
-        <v>0.07480438594593243</v>
+        <v>0.06721407556188808</v>
       </c>
       <c r="AC3">
-        <v>0.1594256697126947</v>
+        <v>-0.07055855716723924</v>
       </c>
       <c r="AD3">
-        <v>0.408</v>
+        <v>0.295</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.408</v>
+        <v>0.295</v>
       </c>
       <c r="AG3">
-        <v>-1.042</v>
+        <v>-1.135</v>
       </c>
       <c r="AH3">
-        <v>0.02871621621621621</v>
+        <v>0.02439024390243902</v>
       </c>
       <c r="AI3">
-        <v>0.05715886803026057</v>
+        <v>0.04479878511769172</v>
       </c>
       <c r="AJ3">
-        <v>-0.08167424361185138</v>
+        <v>-0.1064228785747773</v>
       </c>
       <c r="AK3">
-        <v>-0.1831926863572433</v>
+        <v>-0.2201745877788555</v>
       </c>
       <c r="AL3">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="AM3">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="AN3">
-        <v>0.2193548387096774</v>
+        <v>0.3628536285362854</v>
       </c>
       <c r="AO3">
-        <v>63.125</v>
+        <v>-0.8</v>
       </c>
       <c r="AP3">
-        <v>-0.5602150537634408</v>
+        <v>-1.396063960639607</v>
       </c>
       <c r="AQ3">
-        <v>63.125</v>
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
